--- a/public/plantilla-flujo-caja.xlsx
+++ b/public/plantilla-flujo-caja.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo de Caja" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +115,17 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -311,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -334,53 +345,53 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -428,17 +439,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,13 +477,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,10 +513,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,13 +534,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,7 +550,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -566,14 +577,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -591,6 +602,49 @@
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -959,6 +1013,9 @@
     <col width="25.77734375" customWidth="1" style="37" min="3" max="3"/>
     <col width="22.77734375" customWidth="1" style="37" min="4" max="7"/>
     <col width="25.77734375" customWidth="1" style="37" min="8" max="11"/>
+    <col width="13" customWidth="1" style="37" min="9" max="9"/>
+    <col width="13" customWidth="1" style="37" min="10" max="10"/>
+    <col width="13" customWidth="1" style="37" min="11" max="11"/>
     <col width="17" customWidth="1" style="37" min="12" max="12"/>
     <col width="30.77734375" customWidth="1" style="37" min="13" max="13"/>
   </cols>
@@ -1103,9 +1160,9 @@
       </c>
       <c r="B10" s="100" t="n"/>
       <c r="C10" s="87" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="100" t="n"/>
-      <c r="F10" s="87" t="n"/>
+      <c r="D10" s="108" t="n"/>
+      <c r="E10" s="109" t="n"/>
+      <c r="F10" s="110" t="n"/>
       <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1113,10 +1170,10 @@
       </c>
       <c r="H10" s="100" t="n"/>
       <c r="I10" s="87" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="100" t="n"/>
-      <c r="L10" s="100" t="n"/>
-      <c r="M10" s="87" t="n"/>
+      <c r="J10" s="108" t="n"/>
+      <c r="K10" s="109" t="n"/>
+      <c r="L10" s="109" t="n"/>
+      <c r="M10" s="110" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="37">
       <c r="A11" s="25" t="inlineStr">
@@ -1126,9 +1183,9 @@
       </c>
       <c r="B11" s="100" t="n"/>
       <c r="C11" s="87" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="100" t="n"/>
-      <c r="F11" s="87" t="n"/>
+      <c r="D11" s="108" t="n"/>
+      <c r="E11" s="109" t="n"/>
+      <c r="F11" s="110" t="n"/>
       <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1136,10 +1193,10 @@
       </c>
       <c r="H11" s="100" t="n"/>
       <c r="I11" s="87" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="100" t="n"/>
-      <c r="L11" s="100" t="n"/>
-      <c r="M11" s="87" t="n"/>
+      <c r="J11" s="108" t="n"/>
+      <c r="K11" s="109" t="n"/>
+      <c r="L11" s="109" t="n"/>
+      <c r="M11" s="110" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="37">
       <c r="A12" s="25" t="inlineStr">
@@ -1149,9 +1206,9 @@
       </c>
       <c r="B12" s="100" t="n"/>
       <c r="C12" s="87" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="100" t="n"/>
-      <c r="F12" s="87" t="n"/>
+      <c r="D12" s="108" t="n"/>
+      <c r="E12" s="109" t="n"/>
+      <c r="F12" s="110" t="n"/>
       <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Responsable del control</t>
@@ -1159,10 +1216,10 @@
       </c>
       <c r="H12" s="100" t="n"/>
       <c r="I12" s="87" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="100" t="n"/>
-      <c r="L12" s="100" t="n"/>
-      <c r="M12" s="87" t="n"/>
+      <c r="J12" s="108" t="n"/>
+      <c r="K12" s="109" t="n"/>
+      <c r="L12" s="109" t="n"/>
+      <c r="M12" s="110" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">
       <c r="A13" s="43" t="inlineStr">
@@ -1251,35 +1308,35 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="37">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="111" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="9">
+      <c r="B15" s="112" t="n"/>
+      <c r="C15" s="113">
         <f>IF(K14&lt;&gt;"",K14,IF(J14&lt;&gt;"",J14,""))</f>
         <v/>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="9">
+      <c r="D15" s="114" t="n"/>
+      <c r="E15" s="114" t="n"/>
+      <c r="F15" s="114" t="n"/>
+      <c r="G15" s="114" t="n"/>
+      <c r="H15" s="113">
         <f>IF(AND(D15="",F15=""),"",N(D15)-N(F15))</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="113">
         <f>IF(AND(E15="",G15=""),"",N(E15)-N(G15))</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="113">
         <f>IF(AND(D15="",F15=""),"",N(C15)+N(D15)-N(F15))</f>
         <v/>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="113">
         <f>IF(I15="","",N(C15)+I15)</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="113">
         <f>IF(OR(J15="",K15=""),"",K15-J15)</f>
         <v/>
       </c>
@@ -1289,35 +1346,35 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="37">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="9">
+      <c r="B16" s="112" t="n"/>
+      <c r="C16" s="113">
         <f>IF(K15&lt;&gt;"",K15,IF(J15&lt;&gt;"",J15,""))</f>
         <v/>
       </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="9">
+      <c r="D16" s="114" t="n"/>
+      <c r="E16" s="114" t="n"/>
+      <c r="F16" s="114" t="n"/>
+      <c r="G16" s="114" t="n"/>
+      <c r="H16" s="113">
         <f>IF(AND(D16="",F16=""),"",N(D16)-N(F16))</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="113">
         <f>IF(AND(E16="",G16=""),"",N(E16)-N(G16))</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="113">
         <f>IF(AND(D16="",F16=""),"",IF(J15="",N(C16),J15)+N(D16)-N(F16))</f>
         <v/>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="113">
         <f>IF(I16="","",IF(K15&lt;&gt;"",K15,IF(J15&lt;&gt;"",J15,N(C16)))+I16)</f>
         <v/>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="113">
         <f>IF(OR(J16="",K16=""),"",K16-J16)</f>
         <v/>
       </c>
@@ -1327,35 +1384,35 @@
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="37">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="9">
+      <c r="B17" s="112" t="n"/>
+      <c r="C17" s="113">
         <f>IF(K16&lt;&gt;"",K16,IF(J16&lt;&gt;"",J16,""))</f>
         <v/>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="9">
+      <c r="D17" s="114" t="n"/>
+      <c r="E17" s="114" t="n"/>
+      <c r="F17" s="114" t="n"/>
+      <c r="G17" s="114" t="n"/>
+      <c r="H17" s="113">
         <f>IF(AND(D17="",F17=""),"",N(D17)-N(F17))</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="113">
         <f>IF(AND(E17="",G17=""),"",N(E17)-N(G17))</f>
         <v/>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="113">
         <f>IF(AND(D17="",F17=""),"",IF(J16="",N(C17),J16)+N(D17)-N(F17))</f>
         <v/>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="113">
         <f>IF(I17="","",IF(K16&lt;&gt;"",K16,IF(J16&lt;&gt;"",J16,N(C17)))+I17)</f>
         <v/>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="113">
         <f>IF(OR(J17="",K17=""),"",K17-J17)</f>
         <v/>
       </c>
@@ -1365,35 +1422,35 @@
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="37">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="9">
+      <c r="B18" s="112" t="n"/>
+      <c r="C18" s="113">
         <f>IF(K17&lt;&gt;"",K17,IF(J17&lt;&gt;"",J17,""))</f>
         <v/>
       </c>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="9">
+      <c r="D18" s="114" t="n"/>
+      <c r="E18" s="114" t="n"/>
+      <c r="F18" s="114" t="n"/>
+      <c r="G18" s="114" t="n"/>
+      <c r="H18" s="113">
         <f>IF(AND(D18="",F18=""),"",N(D18)-N(F18))</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="113">
         <f>IF(AND(E18="",G18=""),"",N(E18)-N(G18))</f>
         <v/>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="113">
         <f>IF(AND(D18="",F18=""),"",IF(J17="",N(C18),J17)+N(D18)-N(F18))</f>
         <v/>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="113">
         <f>IF(I18="","",IF(K17&lt;&gt;"",K17,IF(J17&lt;&gt;"",J17,N(C18)))+I18)</f>
         <v/>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="113">
         <f>IF(OR(J18="",K18=""),"",K18-J18)</f>
         <v/>
       </c>
@@ -1403,35 +1460,35 @@
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="37">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="9">
+      <c r="B19" s="112" t="n"/>
+      <c r="C19" s="113">
         <f>IF(K18&lt;&gt;"",K18,IF(J18&lt;&gt;"",J18,""))</f>
         <v/>
       </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="9">
+      <c r="D19" s="114" t="n"/>
+      <c r="E19" s="114" t="n"/>
+      <c r="F19" s="114" t="n"/>
+      <c r="G19" s="114" t="n"/>
+      <c r="H19" s="113">
         <f>IF(AND(D19="",F19=""),"",N(D19)-N(F19))</f>
         <v/>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="113">
         <f>IF(AND(E19="",G19=""),"",N(E19)-N(G19))</f>
         <v/>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="113">
         <f>IF(AND(D19="",F19=""),"",IF(J18="",N(C19),J18)+N(D19)-N(F19))</f>
         <v/>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="113">
         <f>IF(I19="","",IF(K18&lt;&gt;"",K18,IF(J18&lt;&gt;"",J18,N(C19)))+I19)</f>
         <v/>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="113">
         <f>IF(OR(J19="",K19=""),"",K19-J19)</f>
         <v/>
       </c>
@@ -1441,35 +1498,35 @@
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="37">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="111" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="9">
+      <c r="B20" s="112" t="n"/>
+      <c r="C20" s="113">
         <f>IF(K19&lt;&gt;"",K19,IF(J19&lt;&gt;"",J19,""))</f>
         <v/>
       </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="9">
+      <c r="D20" s="114" t="n"/>
+      <c r="E20" s="114" t="n"/>
+      <c r="F20" s="114" t="n"/>
+      <c r="G20" s="114" t="n"/>
+      <c r="H20" s="113">
         <f>IF(AND(D20="",F20=""),"",N(D20)-N(F20))</f>
         <v/>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="113">
         <f>IF(AND(E20="",G20=""),"",N(E20)-N(G20))</f>
         <v/>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="113">
         <f>IF(AND(D20="",F20=""),"",IF(J19="",N(C20),J19)+N(D20)-N(F20))</f>
         <v/>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="113">
         <f>IF(I20="","",IF(K19&lt;&gt;"",K19,IF(J19&lt;&gt;"",J19,N(C20)))+I20)</f>
         <v/>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="113">
         <f>IF(OR(J20="",K20=""),"",K20-J20)</f>
         <v/>
       </c>
@@ -1479,35 +1536,35 @@
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="37">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="111" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="9">
+      <c r="B21" s="112" t="n"/>
+      <c r="C21" s="113">
         <f>IF(K20&lt;&gt;"",K20,IF(J20&lt;&gt;"",J20,""))</f>
         <v/>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="9">
+      <c r="D21" s="114" t="n"/>
+      <c r="E21" s="114" t="n"/>
+      <c r="F21" s="114" t="n"/>
+      <c r="G21" s="114" t="n"/>
+      <c r="H21" s="113">
         <f>IF(AND(D21="",F21=""),"",N(D21)-N(F21))</f>
         <v/>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="113">
         <f>IF(AND(E21="",G21=""),"",N(E21)-N(G21))</f>
         <v/>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="113">
         <f>IF(AND(D21="",F21=""),"",IF(J20="",N(C21),J20)+N(D21)-N(F21))</f>
         <v/>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="113">
         <f>IF(I21="","",IF(K20&lt;&gt;"",K20,IF(J20&lt;&gt;"",J20,N(C21)))+I21)</f>
         <v/>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="113">
         <f>IF(OR(J21="",K21=""),"",K21-J21)</f>
         <v/>
       </c>
@@ -1517,35 +1574,35 @@
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="37">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="111" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="9">
+      <c r="B22" s="112" t="n"/>
+      <c r="C22" s="113">
         <f>IF(K21&lt;&gt;"",K21,IF(J21&lt;&gt;"",J21,""))</f>
         <v/>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="9">
+      <c r="D22" s="114" t="n"/>
+      <c r="E22" s="114" t="n"/>
+      <c r="F22" s="114" t="n"/>
+      <c r="G22" s="114" t="n"/>
+      <c r="H22" s="113">
         <f>IF(AND(D22="",F22=""),"",N(D22)-N(F22))</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="113">
         <f>IF(AND(E22="",G22=""),"",N(E22)-N(G22))</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="113">
         <f>IF(AND(D22="",F22=""),"",IF(J21="",N(C22),J21)+N(D22)-N(F22))</f>
         <v/>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="113">
         <f>IF(I22="","",IF(K21&lt;&gt;"",K21,IF(J21&lt;&gt;"",J21,N(C22)))+I22)</f>
         <v/>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="113">
         <f>IF(OR(J22="",K22=""),"",K22-J22)</f>
         <v/>
       </c>
@@ -1555,35 +1612,35 @@
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="37">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="111" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="9">
+      <c r="B23" s="112" t="n"/>
+      <c r="C23" s="113">
         <f>IF(K22&lt;&gt;"",K22,IF(J22&lt;&gt;"",J22,""))</f>
         <v/>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="9">
+      <c r="D23" s="114" t="n"/>
+      <c r="E23" s="114" t="n"/>
+      <c r="F23" s="114" t="n"/>
+      <c r="G23" s="114" t="n"/>
+      <c r="H23" s="113">
         <f>IF(AND(D23="",F23=""),"",N(D23)-N(F23))</f>
         <v/>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="113">
         <f>IF(AND(E23="",G23=""),"",N(E23)-N(G23))</f>
         <v/>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="113">
         <f>IF(AND(D23="",F23=""),"",IF(J22="",N(C23),J22)+N(D23)-N(F23))</f>
         <v/>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="113">
         <f>IF(I23="","",IF(K22&lt;&gt;"",K22,IF(J22&lt;&gt;"",J22,N(C23)))+I23)</f>
         <v/>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="113">
         <f>IF(OR(J23="",K23=""),"",K23-J23)</f>
         <v/>
       </c>
@@ -1593,35 +1650,35 @@
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="37">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="111" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="9">
+      <c r="B24" s="112" t="n"/>
+      <c r="C24" s="113">
         <f>IF(K23&lt;&gt;"",K23,IF(J23&lt;&gt;"",J23,""))</f>
         <v/>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="9">
+      <c r="D24" s="114" t="n"/>
+      <c r="E24" s="114" t="n"/>
+      <c r="F24" s="114" t="n"/>
+      <c r="G24" s="114" t="n"/>
+      <c r="H24" s="113">
         <f>IF(AND(D24="",F24=""),"",N(D24)-N(F24))</f>
         <v/>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="113">
         <f>IF(AND(E24="",G24=""),"",N(E24)-N(G24))</f>
         <v/>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="113">
         <f>IF(AND(D24="",F24=""),"",IF(J23="",N(C24),J23)+N(D24)-N(F24))</f>
         <v/>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="113">
         <f>IF(I24="","",IF(K23&lt;&gt;"",K23,IF(J23&lt;&gt;"",J23,N(C24)))+I24)</f>
         <v/>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="113">
         <f>IF(OR(J24="",K24=""),"",K24-J24)</f>
         <v/>
       </c>
@@ -1631,35 +1688,35 @@
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="37">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="111" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="9">
+      <c r="B25" s="112" t="n"/>
+      <c r="C25" s="113">
         <f>IF(K24&lt;&gt;"",K24,IF(J24&lt;&gt;"",J24,""))</f>
         <v/>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="9">
+      <c r="D25" s="114" t="n"/>
+      <c r="E25" s="114" t="n"/>
+      <c r="F25" s="114" t="n"/>
+      <c r="G25" s="114" t="n"/>
+      <c r="H25" s="113">
         <f>IF(AND(D25="",F25=""),"",N(D25)-N(F25))</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="113">
         <f>IF(AND(E25="",G25=""),"",N(E25)-N(G25))</f>
         <v/>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="113">
         <f>IF(AND(D25="",F25=""),"",IF(J24="",N(C25),J24)+N(D25)-N(F25))</f>
         <v/>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="113">
         <f>IF(I25="","",IF(K24&lt;&gt;"",K24,IF(J24&lt;&gt;"",J24,N(C25)))+I25)</f>
         <v/>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="113">
         <f>IF(OR(J25="",K25=""),"",K25-J25)</f>
         <v/>
       </c>
@@ -1669,35 +1726,35 @@
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="37">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="111" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="9">
+      <c r="B26" s="112" t="n"/>
+      <c r="C26" s="113">
         <f>IF(K25&lt;&gt;"",K25,IF(J25&lt;&gt;"",J25,""))</f>
         <v/>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="9">
+      <c r="D26" s="114" t="n"/>
+      <c r="E26" s="114" t="n"/>
+      <c r="F26" s="114" t="n"/>
+      <c r="G26" s="114" t="n"/>
+      <c r="H26" s="113">
         <f>IF(AND(D26="",F26=""),"",N(D26)-N(F26))</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="113">
         <f>IF(AND(E26="",G26=""),"",N(E26)-N(G26))</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="113">
         <f>IF(AND(D26="",F26=""),"",IF(J25="",N(C26),J25)+N(D26)-N(F26))</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="113">
         <f>IF(I26="","",IF(K25&lt;&gt;"",K25,IF(J25&lt;&gt;"",J25,N(C26)))+I26)</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="113">
         <f>IF(OR(J26="",K26=""),"",K26-J26)</f>
         <v/>
       </c>
@@ -1714,27 +1771,27 @@
       </c>
       <c r="B27" s="87" t="n"/>
       <c r="C27" s="38" t="n"/>
-      <c r="D27" s="89">
+      <c r="D27" s="115">
         <f>SUM(D15:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="89">
+      <c r="E27" s="115">
         <f>SUM(E15:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="89">
+      <c r="F27" s="115">
         <f>SUM(F15:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="89">
+      <c r="G27" s="115">
         <f>SUM(G15:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="89">
+      <c r="H27" s="115">
         <f>SUM(H15:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="89">
+      <c r="I27" s="115">
         <f>SUM(I15:I26)</f>
         <v/>
       </c>
@@ -1763,7 +1820,7 @@
       <c r="L29" s="100" t="n"/>
       <c r="M29" s="87" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="37">
+    <row r="30" ht="94" customHeight="1" s="37">
       <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Ingresos proyectados del periodo</t>
@@ -1773,12 +1830,12 @@
       <c r="C30" s="100" t="n"/>
       <c r="D30" s="100" t="n"/>
       <c r="E30" s="87" t="n"/>
-      <c r="F30" s="44">
+      <c r="F30" s="116">
         <f>D27</f>
         <v/>
       </c>
       <c r="G30" s="87" t="n"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="I30" s="117" t="inlineStr">
         <is>
           <t>Cómo leerlo:
   El saldo inicial se escribe solo en el primer mes; los siguientes lo arrastran.
@@ -1802,7 +1859,7 @@
       <c r="C31" s="100" t="n"/>
       <c r="D31" s="100" t="n"/>
       <c r="E31" s="87" t="n"/>
-      <c r="F31" s="44">
+      <c r="F31" s="116">
         <f>F27</f>
         <v/>
       </c>
@@ -1820,7 +1877,7 @@
       <c r="C32" s="100" t="n"/>
       <c r="D32" s="100" t="n"/>
       <c r="E32" s="87" t="n"/>
-      <c r="F32" s="44">
+      <c r="F32" s="116">
         <f>IF(COUNT(J15:J26)=0,"",MIN(J15:J26))</f>
         <v/>
       </c>
@@ -1838,7 +1895,7 @@
       <c r="C33" s="100" t="n"/>
       <c r="D33" s="100" t="n"/>
       <c r="E33" s="87" t="n"/>
-      <c r="F33" s="93">
+      <c r="F33" s="118">
         <f>IF(COUNT(J15:J26)=0,"",INDEX(B15:B26,MATCH(MIN(J15:J26),J15:J26,0)))</f>
         <v/>
       </c>
@@ -1856,7 +1913,7 @@
       <c r="C34" s="100" t="n"/>
       <c r="D34" s="100" t="n"/>
       <c r="E34" s="87" t="n"/>
-      <c r="F34" s="44">
+      <c r="F34" s="116">
         <f>IF(COUNT(J15:J26)=0,"",MAX(0,-MIN(J15:J26)))</f>
         <v/>
       </c>
@@ -1874,7 +1931,7 @@
       <c r="C35" s="100" t="n"/>
       <c r="D35" s="100" t="n"/>
       <c r="E35" s="87" t="n"/>
-      <c r="F35" s="83">
+      <c r="F35" s="119">
         <f>IF(SUMIFS(D15:D26,E15:E26,"&lt;&gt;")=0,"",E27/SUMIFS(D15:D26,E15:E26,"&lt;&gt;"))</f>
         <v/>
       </c>
@@ -1936,9 +1993,9 @@
       </c>
       <c r="B39" s="100" t="n"/>
       <c r="C39" s="87" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="100" t="n"/>
-      <c r="F39" s="87" t="n"/>
+      <c r="D39" s="108" t="n"/>
+      <c r="E39" s="109" t="n"/>
+      <c r="F39" s="110" t="n"/>
       <c r="G39" s="25" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1946,10 +2003,10 @@
       </c>
       <c r="H39" s="100" t="n"/>
       <c r="I39" s="87" t="n"/>
-      <c r="J39" s="27" t="n"/>
-      <c r="K39" s="100" t="n"/>
-      <c r="L39" s="100" t="n"/>
-      <c r="M39" s="87" t="n"/>
+      <c r="J39" s="120" t="n"/>
+      <c r="K39" s="109" t="n"/>
+      <c r="L39" s="109" t="n"/>
+      <c r="M39" s="110" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="37">
       <c r="A40" s="25" t="inlineStr">
@@ -1959,9 +2016,9 @@
       </c>
       <c r="B40" s="100" t="n"/>
       <c r="C40" s="87" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="100" t="n"/>
-      <c r="F40" s="87" t="n"/>
+      <c r="D40" s="108" t="n"/>
+      <c r="E40" s="109" t="n"/>
+      <c r="F40" s="110" t="n"/>
       <c r="G40" s="25" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1969,10 +2026,10 @@
       </c>
       <c r="H40" s="100" t="n"/>
       <c r="I40" s="87" t="n"/>
-      <c r="J40" s="27" t="n"/>
-      <c r="K40" s="100" t="n"/>
-      <c r="L40" s="100" t="n"/>
-      <c r="M40" s="87" t="n"/>
+      <c r="J40" s="120" t="n"/>
+      <c r="K40" s="109" t="n"/>
+      <c r="L40" s="109" t="n"/>
+      <c r="M40" s="110" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="37">
       <c r="A41" s="25" t="inlineStr">
@@ -1982,9 +2039,9 @@
       </c>
       <c r="B41" s="100" t="n"/>
       <c r="C41" s="87" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="100" t="n"/>
-      <c r="F41" s="87" t="n"/>
+      <c r="D41" s="108" t="n"/>
+      <c r="E41" s="109" t="n"/>
+      <c r="F41" s="110" t="n"/>
       <c r="G41" s="25" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1992,12 +2049,13 @@
       </c>
       <c r="H41" s="100" t="n"/>
       <c r="I41" s="87" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="100" t="n"/>
-      <c r="L41" s="100" t="n"/>
-      <c r="M41" s="87" t="n"/>
+      <c r="J41" s="120" t="n"/>
+      <c r="K41" s="109" t="n"/>
+      <c r="L41" s="109" t="n"/>
+      <c r="M41" s="110" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="58">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
